--- a/fixtures/daily-cash/테스트_일일자금일보_261013.xlsx
+++ b/fixtures/daily-cash/테스트_일일자금일보_261013.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="118">
   <si>
     <t xml:space="preserve">테스트 일일자금일보
 2026.10.12</t>
@@ -157,6 +157,9 @@
     <t>정기예금 현황(외화)</t>
   </si>
   <si>
+    <t>신탁현황</t>
+  </si>
+  <si>
     <t>주요 집행 내역</t>
   </si>
   <si>
@@ -329,7 +332,7 @@
     <t>최종 확인</t>
   </si>
   <si>
-    <t>확인 4859b739c4cf</t>
+    <t>확인 f9ee2738f662</t>
   </si>
   <si>
     <t>workDate</t>
@@ -413,7 +416,7 @@
     <t>sources</t>
   </si>
   <si>
-    <t>{"previousReport":[{"name":"테스트_전일일보.xlsx","fingerprint":"d3ad1e38321d6c7008c807711e1457fb5284333e425e2a240927b3c45d9cdd42"}],"weeklyPlans":[{"name":"테스트_주간계획.xlsx","fingerprint":"c5b450a26eec38026581d2f7c3c30ee3a85c16c6d343c1a8401eed45f3f093a6"}],"cashStatus":[{"name":"261014_테스트_자금현황표[KC].xlsx","fingerprint":"cebafdaa586226fe57bb5b8f704d069460ffbc7d93f0d6b781806a6d47f25a40"}]}</t>
+    <t>{"previousReport":[{"name":"테스트_전일일보.xlsx","fingerprint":"dfb5fb7a38fd2f48faab86c3ba456e23d409a6d589ad2173fa9df4b5bc04f384"}],"weeklyPlans":[{"name":"테스트_주간계획.xlsx","fingerprint":"e77a91a62f0ded7acf6f41c82315b4e0491b00236fc3e227de007729ac29e0fe"}],"cashStatus":[{"name":"261013_테스트_자금현황표[KC].xlsx","fingerprint":"7777d954775e4c88c2e03324d46f7614654fff60ca22546f6df9c51edd63a925"}]}</t>
   </si>
 </sst>
 </file>
@@ -852,8 +855,8 @@
     <col min="16" max="16" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" hidden="1" spans="7:15" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="22" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +867,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" ht="22" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -873,7 +876,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="22" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -882,8 +885,8 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="22" customHeight="1" hidden="1" spans="7:15" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="22" customHeight="1" hidden="1" spans="7:15" x14ac:dyDescent="0.25"/>
     <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>1</v>
@@ -1852,7 +1855,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="42" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>28</v>
       </c>
@@ -3035,7 +3038,10 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="5"/>
+      <c r="D98" s="5">
+        <f>SUM(D51:D97)</f>
+        <v>0</v>
+      </c>
       <c r="E98" s="5"/>
       <c r="F98" s="4"/>
       <c r="G98" s="5"/>
@@ -3573,7 +3579,10 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="5"/>
+      <c r="D120" s="5">
+        <f>SUM(D102:D119)</f>
+        <v>0</v>
+      </c>
       <c r="E120" s="5"/>
       <c r="F120" s="4"/>
       <c r="G120" s="5"/>
@@ -3599,13 +3608,15 @@
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
     </row>
-    <row r="122" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
+    <row r="122" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
-      <c r="F122" s="4"/>
+      <c r="F122" s="5"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="4"/>
@@ -3683,7 +3694,10 @@
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
-      <c r="D126" s="5"/>
+      <c r="D126" s="5">
+        <f>SUM(D124:D125)</f>
+        <v>0</v>
+      </c>
       <c r="E126" s="5"/>
       <c r="F126" s="4"/>
       <c r="G126" s="5"/>
@@ -3711,7 +3725,7 @@
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -3743,15 +3757,15 @@
     </row>
     <row r="130" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F130" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="F130" s="5"/>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
       <c r="I130" s="4"/>
@@ -3762,13 +3776,13 @@
     </row>
     <row r="131" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
@@ -4159,13 +4173,13 @@
     </row>
     <row r="157" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
@@ -5350,7 +5364,10 @@
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
-      <c r="D236" s="5"/>
+      <c r="D236" s="5">
+        <f>SUM(D157:D235)</f>
+        <v>0</v>
+      </c>
       <c r="E236" s="5"/>
       <c r="F236" s="4"/>
       <c r="G236" s="5"/>
@@ -5363,15 +5380,15 @@
     </row>
     <row r="237" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
       <c r="D237" s="5"/>
       <c r="E237" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F237" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="F237" s="5"/>
       <c r="G237" s="5"/>
       <c r="H237" s="5"/>
       <c r="I237" s="4"/>
@@ -5395,7 +5412,7 @@
       <c r="L238" s="4"/>
       <c r="M238" s="4"/>
       <c r="O238" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="239" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5413,7 +5430,7 @@
       <c r="L239" s="4"/>
       <c r="M239" s="4"/>
       <c r="O239" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="240" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5431,7 +5448,7 @@
       <c r="L240" s="4"/>
       <c r="M240" s="4"/>
       <c r="O240" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="241" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5441,13 +5458,13 @@
       <c r="D241" s="5"/>
       <c r="E241" s="5"/>
       <c r="F241" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I241" s="4"/>
       <c r="J241" s="4"/>
@@ -5455,7 +5472,7 @@
       <c r="L241" s="4"/>
       <c r="M241" s="4"/>
       <c r="O241" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="242" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5473,7 +5490,7 @@
       <c r="L242" s="4"/>
       <c r="M242" s="4"/>
       <c r="O242" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="243" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5483,13 +5500,13 @@
       <c r="D243" s="5"/>
       <c r="E243" s="5"/>
       <c r="F243" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H243" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I243" s="4"/>
       <c r="J243" s="4"/>
@@ -5497,7 +5514,7 @@
       <c r="L243" s="4"/>
       <c r="M243" s="4"/>
       <c r="O243" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="244" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5515,7 +5532,7 @@
       <c r="L244" s="4"/>
       <c r="M244" s="4"/>
       <c r="O244" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="245" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5525,13 +5542,13 @@
       <c r="D245" s="5"/>
       <c r="E245" s="5"/>
       <c r="F245" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I245" s="4"/>
       <c r="J245" s="4"/>
@@ -5539,7 +5556,7 @@
       <c r="L245" s="4"/>
       <c r="M245" s="4"/>
       <c r="O245" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="246" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5557,7 +5574,7 @@
       <c r="L246" s="4"/>
       <c r="M246" s="4"/>
       <c r="O246" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="247" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5567,13 +5584,13 @@
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
       <c r="F247" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
@@ -5581,7 +5598,7 @@
       <c r="L247" s="3"/>
       <c r="M247" s="3"/>
       <c r="O247" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="248" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5599,22 +5616,26 @@
       <c r="L248" s="4"/>
       <c r="M248" s="4"/>
       <c r="O248" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="249" spans="7:15" x14ac:dyDescent="0.25">
       <c r="O249" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="216">
+  <mergeCells count="222">
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A100:G100"/>
+    <mergeCell ref="A122:G122"/>
     <mergeCell ref="A128:G128"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="E130:G130"/>
     <mergeCell ref="B131:C131"/>
     <mergeCell ref="F131:G131"/>
     <mergeCell ref="B132:C132"/>
@@ -5825,6 +5846,8 @@
     <mergeCell ref="F234:G234"/>
     <mergeCell ref="B235:C235"/>
     <mergeCell ref="F235:G235"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="E237:G237"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -5851,10 +5874,10 @@
     <col min="16" max="16" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" hidden="1" spans="7:15" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
@@ -5863,7 +5886,7 @@
       <c r="G2"/>
       <c r="H2"/>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
@@ -5872,7 +5895,7 @@
       <c r="G3"/>
       <c r="H3"/>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
@@ -5881,9 +5904,9 @@
       <c r="G4"/>
       <c r="H4"/>
     </row>
-    <row r="5" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="22" customHeight="1" hidden="1" spans="7:15" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="22" customHeight="1" hidden="1" spans="7:15" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -5900,7 +5923,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
@@ -5968,7 +5991,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
@@ -6158,7 +6181,7 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -6200,7 +6223,7 @@
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -6216,10 +6239,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>2</v>
       </c>
@@ -6260,7 +6283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
@@ -6298,7 +6321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -6328,7 +6351,7 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
@@ -6404,7 +6427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -6434,7 +6457,7 @@
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4" t="s">
@@ -6472,7 +6495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -6502,7 +6525,7 @@
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4" t="s">
@@ -6540,7 +6563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -6570,7 +6593,7 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4" t="s">
@@ -6608,7 +6631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -6997,7 +7020,7 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>27</v>
       </c>
@@ -7014,7 +7037,7 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
@@ -7055,11 +7078,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="42" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B51" s="4"/>
+      <c r="B51"/>
       <c r="C51" s="4" t="s">
         <v>29</v>
       </c>
@@ -8235,7 +8258,7 @@
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
     </row>
-    <row r="98" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -8277,7 +8300,7 @@
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
     </row>
-    <row r="100" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>30</v>
       </c>
@@ -8293,10 +8316,10 @@
       <c r="K100" s="3"/>
       <c r="L100" s="3"/>
       <c r="M100" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>2</v>
       </c>
@@ -8985,7 +9008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -9030,14 +9053,16 @@
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
     </row>
-    <row r="122" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="5"/>
+    <row r="122" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
       <c r="H122" s="5"/>
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
@@ -9152,9 +9177,9 @@
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
     </row>
-    <row r="128" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B128"/>
       <c r="C128"/>
@@ -9184,20 +9209,20 @@
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
     </row>
-    <row r="130" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="B130"/>
+      <c r="C130"/>
       <c r="D130" s="5">
         <v>100000</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F130" s="4"/>
-      <c r="G130" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="F130"/>
+      <c r="G130"/>
       <c r="H130" s="5">
         <v>109000</v>
       </c>
@@ -9207,19 +9232,19 @@
       <c r="L130" s="4"/>
       <c r="M130" s="4"/>
     </row>
-    <row r="131" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C131"/>
       <c r="D131" s="5">
         <v>10000</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F131" s="5"/>
       <c r="G131"/>
@@ -9590,7 +9615,7 @@
       <c r="L155" s="4"/>
       <c r="M155" s="4"/>
     </row>
-    <row r="156" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156"/>
@@ -9611,22 +9636,22 @@
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
     </row>
-    <row r="157" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C157"/>
       <c r="D157" s="5">
         <v>1000</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G157"/>
       <c r="H157" s="5">
@@ -10808,7 +10833,7 @@
       <c r="L235" s="4"/>
       <c r="M235" s="4"/>
     </row>
-    <row r="236" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -10829,21 +10854,21 @@
       <c r="L236" s="4"/>
       <c r="M236" s="4"/>
     </row>
-    <row r="237" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B237" s="4"/>
-      <c r="C237" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="B237"/>
+      <c r="C237"/>
       <c r="D237" s="5">
         <f>D130+D156-D236</f>
         <v>109000</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F237" s="4"/>
-      <c r="G237" s="5"/>
+        <v>69</v>
+      </c>
+      <c r="F237"/>
+      <c r="G237"/>
       <c r="H237" s="5">
         <f>H130+H156-H236</f>
         <v>107000</v>
@@ -10854,7 +10879,7 @@
       <c r="L237" s="4"/>
       <c r="M237" s="4"/>
     </row>
-    <row r="238" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -10869,10 +10894,10 @@
       <c r="L238" s="4"/>
       <c r="M238" s="4"/>
       <c r="O238" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="239" ht="22" customHeight="1" hidden="1" spans="1:16" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="239" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -10887,13 +10912,13 @@
       <c r="L239" s="4"/>
       <c r="M239" s="4"/>
       <c r="O239" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P239">
         <v>0</v>
       </c>
     </row>
-    <row r="240" ht="22" customHeight="1" hidden="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -10908,7 +10933,7 @@
       <c r="L240" s="4"/>
       <c r="M240" s="4"/>
       <c r="O240" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P240">
         <v>0</v>
@@ -10921,13 +10946,13 @@
       <c r="D241" s="5"/>
       <c r="E241" s="5"/>
       <c r="F241" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I241" s="4"/>
       <c r="J241" s="4"/>
@@ -10935,7 +10960,7 @@
       <c r="L241" s="4"/>
       <c r="M241" s="4"/>
       <c r="O241" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P241">
         <v>0</v>
@@ -10963,7 +10988,7 @@
       <c r="L242" s="4"/>
       <c r="M242" s="4"/>
       <c r="O242" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P242">
         <v>0</v>
@@ -10976,13 +11001,13 @@
       <c r="D243" s="5"/>
       <c r="E243" s="5"/>
       <c r="F243" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H243" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I243" s="4"/>
       <c r="J243" s="4"/>
@@ -10990,7 +11015,7 @@
       <c r="L243" s="4"/>
       <c r="M243" s="4"/>
       <c r="O243" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P243">
         <v>0</v>
@@ -11018,7 +11043,7 @@
       <c r="L244" s="4"/>
       <c r="M244" s="4"/>
       <c r="O244" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P244">
         <v>0</v>
@@ -11031,13 +11056,13 @@
       <c r="D245" s="5"/>
       <c r="E245" s="5"/>
       <c r="F245" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I245" s="4"/>
       <c r="J245" s="4"/>
@@ -11045,7 +11070,7 @@
       <c r="L245" s="4"/>
       <c r="M245" s="4"/>
       <c r="O245" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P245">
         <v>0</v>
@@ -11073,7 +11098,7 @@
       <c r="L246" s="4"/>
       <c r="M246" s="4"/>
       <c r="O246" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P246">
         <v>0</v>
@@ -11086,13 +11111,13 @@
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
       <c r="F247" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
@@ -11100,7 +11125,7 @@
       <c r="L247" s="3"/>
       <c r="M247" s="3"/>
       <c r="O247" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P247">
         <v>0</v>
@@ -11128,7 +11153,7 @@
       <c r="L248" s="4"/>
       <c r="M248" s="4"/>
       <c r="O248" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P248">
         <v>0</v>
@@ -11136,20 +11161,24 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="O249" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P249">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="216">
+  <mergeCells count="222">
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A100:G100"/>
+    <mergeCell ref="A122:G122"/>
     <mergeCell ref="A128:G128"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="E130:G130"/>
     <mergeCell ref="B131:C131"/>
     <mergeCell ref="F131:G131"/>
     <mergeCell ref="B132:C132"/>
@@ -11360,6 +11389,8 @@
     <mergeCell ref="F234:G234"/>
     <mergeCell ref="B235:C235"/>
     <mergeCell ref="F235:G235"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="E237:G237"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -11378,210 +11409,210 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
